--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-11-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_17-11-2025.xlsx
@@ -592,23 +592,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -712,23 +712,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -832,23 +832,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -952,23 +952,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1072,23 +1072,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1192,23 +1192,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1258,19 +1258,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>£20.25</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>£20.25</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>£20.47</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>£20.47</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>£20.47</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>£20.75</t>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£20.53</t>
+          <t>£20.43</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1312,23 +1312,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1432,23 +1432,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1552,23 +1552,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.20</t>
+          <t>£25.12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1672,23 +1672,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1738,12 +1738,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£33.00</t>
+          <t>£32.15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£33.00</t>
+          <t>£32.15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1792,23 +1792,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1912,23 +1912,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -1978,12 +1978,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>£38.05</t>
+          <t>£37.70</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>£38.05</t>
+          <t>£37.70</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2032,23 +2032,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2152,23 +2152,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£37.72</t>
+          <t>£37.65</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£37.72</t>
+          <t>£37.65</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2272,23 +2272,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2489,23 +2489,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2609,23 +2609,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2729,23 +2729,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2849,23 +2849,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -2969,23 +2969,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3089,23 +3089,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3209,23 +3209,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3329,23 +3329,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
@@ -3449,23 +3449,23 @@
   (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	0x7ff7c577a235
-	0x7ff7c54d2650
-	0x7ff7c52616dd
-	0x7ff7c52ba27e
-	0x7ff7c52ba58c
-	0x7ff7c530ed77
-	0x7ff7c530baba
-	0x7ff7c52ab0ed
-	0x7ff7c52abf63
-	0x7ff7c57a5d60
-	0x7ff7c579fe8a
-	0x7ff7c57c1005
-	0x7ff7c54ed73e
-	0x7ff7c54f4e3f
-	0x7ff7c54db7e4
-	0x7ff7c54db99f
-	0x7ff7c54c1908
+	0x7ff720c4a235
+	0x7ff7209a2650
+	0x7ff7207316dd
+	0x7ff72078a27e
+	0x7ff72078a58c
+	0x7ff7207ded77
+	0x7ff7207dbaba
+	0x7ff72077b0ed
+	0x7ff72077bf63
+	0x7ff720c75d60
+	0x7ff720c6fe8a
+	0x7ff720c91005
+	0x7ff7209bd73e
+	0x7ff7209c4e3f
+	0x7ff7209ab7e4
+	0x7ff7209ab99f
+	0x7ff720991908
 	0x7fff71bce8d7
 	0x7fff72a2c53c
 </t>
